--- a/customer_service_forms/012_fashion_retail_customer_service_report--customer_service_forms.xlsx
+++ b/customer_service_forms/012_fashion_retail_customer_service_report--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'order_issue'}</t>
+          <t>order_issue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Order Issue'}</t>
+          <t>Order Issue</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'product_return'}</t>
+          <t>product_return</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Product Return'}</t>
+          <t>Product Return</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'customer_complaint'}</t>
+          <t>customer_complaint</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Customer Complaint'}</t>
+          <t>Customer Complaint</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'awaiting_response'}</t>
+          <t>awaiting_response</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Awaiting Response'}</t>
+          <t>Awaiting Response</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'successful_resolution'}</t>
+          <t>successful_resolution</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Successful Resolution'}</t>
+          <t>Successful Resolution</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'customer_satisfied'}</t>
+          <t>customer_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Customer Satisfied'}</t>
+          <t>Customer Satisfied</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'improvement'}</t>
+          <t>improvement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Improvement'}</t>
+          <t>Improvement</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'sales_associate'}</t>
+          <t>sales_associate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Sales Associate'}</t>
+          <t>Sales Associate</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'customer_support'}</t>
+          <t>customer_support</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Customer Support'}</t>
+          <t>Customer Support</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'store_manager'}</t>
+          <t>store_manager</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Store Manager'}</t>
+          <t>Store Manager</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'regional_manager'}</t>
+          <t>regional_manager</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Regional Manager'}</t>
+          <t>Regional Manager</t>
         </is>
       </c>
     </row>
